--- a/Estructurado en tabla.xlsx
+++ b/Estructurado en tabla.xlsx
@@ -1,26 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Proyecto TICs\Estructurador de verdad\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD436694-718B-4C96-8FD3-BEE784B8DEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D77195-F8B4-4AEF-805F-E1BD5F43875D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="1140" windowWidth="12360" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5355" yWindow="270" windowWidth="13230" windowHeight="10545" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
+    <sheet name="Auditoría" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2279" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4060" uniqueCount="232">
   <si>
     <t>Fecha de los Hechos</t>
   </si>
@@ -298,8 +299,7 @@
     <t>31 - FISCALIA 31</t>
   </si>
   <si>
-    <t>DIRECCIÓN SECCIONAL DE BOGOTÁ -UNIDAD HURTOS - ESTABLECIMIENTO 
-COMERCIAL</t>
+    <t>DIRECCIÓN SECCIONAL DE BOGOTÁ -UNIDAD HURTOS - ESTABLECIMIENTO COMERCIAL</t>
   </si>
   <si>
     <t>HURTO. ART. 239 C.P.</t>
@@ -317,346 +317,406 @@
     <t>1 - BOGOTÁ, D.C.</t>
   </si>
   <si>
+    <t>Ciudad Berna, Antonio Narino, Bogotá, D.C.</t>
+  </si>
+  <si>
+    <t>¿Qué viene a denunciar? HURTO CALIFICADO. ARTICULO 240. ¿Cómo le pasó? FormalizaciónAtraco a mano armadaTienda D1: Ciudad BernaCódigo: 6A080227Dirección: CRA 14 # 6 sur -34Localidad: Antonio NariñoFecha: 06 -06-2024Hora: 19:36 ¿ 19:37Quien reporta: Supervis ora punto de ventaNombre: Allison Carvajal Estrada CC: 1.013.676.828 de BogotáN° Cel: 3142421604Dirección residencia: CRA 12 A # 2 -34 surBarrio: Sevilla Descripción del sujeto: 1.70 Mts aproximadamente de estatura tez blanca, Vestía Jean de color azul, cha queta impermeable de color azul oscuro, tenis de color gris, gorra azul oscuro con logo de YANKIES (portaba arma de fuego tipo pistola). Delincuente plenamente identificado como: Diego Fernando Rativa CC: 1.001.047.057.Hechos:Ingresa el sujeto anteriorment e descrito al piso de ventas, se dirige directamente a la POS 3 aprovechando que la Asistente le va a entregar vueltas a una cliente, la intimida con un arma de fuego tipo pistola, la obliga abrir la tapa de la POS, logra extraer el dinero producto de las ventas, sale de la tienda caminando y emprende la huida con rumbo desconocido por la avenida Caracas sentido norte - surSe encontraba en la POS 3Nombre: Angie Tatiana Jimenez GomezC.C: 1.000.121.985 de BogotáDirección: CRA 5 este # 36B sur -49Barrio: La Vic toriaCel: 3247856370Afectaciones:Dinero:POS 3: $1'073.000Total: $1'073.000Personal y cliente ilesosLlega cuadrante Berna al mando del Intendente Orlando Sánchez Cel: 3017533464No llega Unidad Investigativa</t>
+  </si>
+  <si>
+    <t>ACTIVO</t>
+  </si>
+  <si>
+    <t>INDAGACIÓN</t>
+  </si>
+  <si>
+    <t>VIGENTE</t>
+  </si>
+  <si>
+    <t>Ley 906</t>
+  </si>
+  <si>
+    <t>SI</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>DENUNCIA</t>
+  </si>
+  <si>
+    <t>NINGUNO</t>
+  </si>
+  <si>
+    <t>DENUNCIANTE</t>
+  </si>
+  <si>
+    <t>CÉDULA DE CIUDADANÍA</t>
+  </si>
+  <si>
+    <t>1000121985</t>
+  </si>
+  <si>
+    <t>JIMENEZ GOMEZ ANGIE TATIANA</t>
+  </si>
+  <si>
+    <t>3124623005</t>
+  </si>
+  <si>
+    <t>jorge.morales@d1.com.co</t>
+  </si>
+  <si>
+    <t>VICTIMA</t>
+  </si>
+  <si>
+    <t>08/12/2023 05:23:00</t>
+  </si>
+  <si>
+    <t>050016099166202411569</t>
+  </si>
+  <si>
+    <t>100141 - DIRECCIÓN SECCIONAL DE MEDELLÍN</t>
+  </si>
+  <si>
+    <t>500141034 - UNIDAD ESTAFAS - MEDELLIN</t>
+  </si>
+  <si>
+    <t>111 - FISCALIA 111</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN SECCIONAL DE MEDELLÍN -UNIDAD ESTAFAS - MEDELLIN</t>
+  </si>
+  <si>
+    <t>ESTAFA. ART. 246 C.P. MENOR CUANTIA</t>
+  </si>
+  <si>
+    <t>BIENES MUEBLES</t>
+  </si>
+  <si>
+    <t>COMPRA</t>
+  </si>
+  <si>
+    <t>PERSONAL SUPLANTACIÓN</t>
+  </si>
+  <si>
+    <t>1 - MEDELLÍN</t>
+  </si>
+  <si>
+    <t>05001 (MEDELLÍN)</t>
+  </si>
+  <si>
+    <t>¿Qué viene a denunciar? ESTAFA ART. 246 SE LE ENVIA LINK DE SUIP AL CORREO ELECTRÓNICO DEL USUARIO PARA QUE MEDIANTE AUTOGESTIÓN FINALICE EL REGISTRO DE SU DENUNCIA ¿Cómo le pasó? SE COMPRO LA MOTOCICLETA MARCA HONDA XRE 300 MODELO 2020 CON PLACAS SDA95F AL SEÑOR ESTIVEN CARTAGENA HERNANDEZ CC 1001738290 DOMICILIADO EN LA CRA 78 NRO 2B 174 BARRIO BELEN TELEFONO 3045506549, EL DIA 08/12/2023 MOMENTO EN EL CUAL EL SEÑOR ENTREGA CON LA MOTOCICLETA LOS TRASPASOS DE PROPIEDAD FIRMADOS Y AUTENTICADOS POR EL PROP IETARIO ANDRES RODRIGUEZ DIAZ, EL SEÑOR CARTAGENA HERNANDEZ RECIBIO LA SUMA DE $16.750.000 ADEMAS DE $428.000 DE LOS GASTOS DEL TRASPASO, $243.000 PARA EL PAGO DEL IMPUESTO AUTOMOTOR DE LA MOTOCICLETA Y $250.000 DESTINADOS PARA EL CAMBIO DE UN REPUESTO DE LA MOTOCICLETA, EN SU MOMENTO EL SEÑOR CARTAGENA HERNANDEZ ADUJO QUE EL GARANTIZABA LA PROCEDENCIA DEL VEHICULO YA QUE SIEMPRE HABIA SIDO DE SU PROPIEDAD PERO POSTERIORMENTE FUE SINCERO Y DIJO QUE LA MOTOCICLETA LA HABIA COMPRADO EL 17/11/2023 EN LA CIUDAD DE IBAGUE MOMENTO EN QUE REALIZO UNA COMPRAVENTA AUTOTENTICADA POR LA NOTARIA SEPTIMA DEL CIRCUITO. EL NEGOCIO TUVO LUGAR EN LA CRA 80 CON CALLE 2A AL FRENTE DE LA CLINICA LAS AMERICAS DE LA 80. EL PASADO LUNES 7 DE ENERO EN UN CONTROL POLICIAL SE REVISAN LOS ANTECEDENTES DE LA MOTOCICLETA ENCONTRANDO QUE EL VEHICULO TIENE UN DENUNCIO POR HURTO EN LA FISCALIA 89 SECCIONAL BOGOTA CON NOTICIA CRIMINAL 110016101523202304732 POR LO QUE EL VEHICULO FUE CONDUCIDO A LA ESTACION DE POLICIA DEL MUNICIPIO DE YARUMAL ANTIOQUIA PARA SER PUESTO A DISPOSICION DE LA AUTORIDAD COMPETENTE, A PESAR DE HABER TRATADO DE LLEGAR A UN ACUERDO CON EL SEÑOR CARTAGENA HERNANDEZ NO SE HA PODIDO.</t>
+  </si>
+  <si>
+    <t>INDICIADO</t>
+  </si>
+  <si>
+    <t>1001738290</t>
+  </si>
+  <si>
+    <t>CARTAGENA HERNANDEZ STEVEN</t>
+  </si>
+  <si>
+    <t>QUERELLABLE</t>
+  </si>
+  <si>
+    <t>QUERELLA</t>
+  </si>
+  <si>
+    <t>1018347478</t>
+  </si>
+  <si>
+    <t>ACEVEDO ESTRADA JAIME ANDRES</t>
+  </si>
+  <si>
+    <t>- null</t>
+  </si>
+  <si>
+    <t>3127382816</t>
+  </si>
+  <si>
+    <t>ACPM992@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>TESTIGO</t>
+  </si>
+  <si>
+    <t>1042770387</t>
+  </si>
+  <si>
+    <t>MESA MOLINA LEIDY YULIANA</t>
+  </si>
+  <si>
+    <t>02/11/2707 00:66:99</t>
+  </si>
+  <si>
+    <t>043974444559914117935</t>
+  </si>
+  <si>
+    <t>883535 - JOHQATJGW SGWKLUXUV IH KTZSHE</t>
+  </si>
+  <si>
+    <t>3375852755 - PXYFXN IDZJZK - UIVGGKDYRFMQBBU JDWQBSIVU</t>
+  </si>
+  <si>
+    <t>93 - WGJJGYZY 02</t>
+  </si>
+  <si>
+    <t>BGRJHRZOR VEPQREJFE AH AMNGRX -ONYDEW ALPTCR - ULBVXGXSQUPBSIB RDHEELJVP</t>
+  </si>
+  <si>
+    <t>RKCLE. HVA. 447 J.Q.</t>
+  </si>
+  <si>
+    <t>DUHMR Y HLBYOMOMIPCVIIKQ</t>
+  </si>
+  <si>
+    <t>XMHWKK</t>
+  </si>
+  <si>
+    <t>NTCB OY UWABY</t>
+  </si>
+  <si>
+    <t>7 - YXWTRO, N.Y.</t>
+  </si>
+  <si>
+    <t>05176 DCMVJM/SSUNHCGXW/OYRLIW:ANTUBM RMIKV/JSUHEDBBG ESOMFFC LEPWKA,SVTKFP, G.C./HUUIDB, X.B.,PBOIPO DKCYB</t>
+  </si>
+  <si>
+    <t>¿Bul jivjj t iifviwrvp? HLMTY IVZHKBIDEJ. SEJXHTOZ 289. ¿Qouu yn bpjx? TacuganzzvyhjZgqrtn b jerf maiakrTglbek T5: Jfhyou OotwoDpkzvd: 0Y827338Oelghvonu: KWK 76 # 3 bjg -36Xcujaacfy: Fwqlxds EjztxgUkchv: 75 -45-1709Fzvx: 35:71 ¿ 98:33Kdkja aizuzep: Drquaxls kgk cegym dk pwmmfUfxaoo: Jrhnair Bsngmxqv Hjxkqgw NB: 3.786.054.219 cp WbjegoA° Yok: 4108787121Bebhdtwjn dkggzwbmhz: JEM 73 G # 3 -82 kknWbcjbh: Envchsn Cimpongkhfz ylu wziewv: 3.34 Trc gewzkqubslmvtwy oc yygexdvr wti boqvue, Iacqfj Usox ya anxqq yzig, gqu jeomp rzdcjnxbxoa xt mdwmu utci fiotym, wujzg xe owbdk tylc, nmrvo pcmb rkriqd gzd raoe th THXHPOB (gqhxjiq wnqr yd mkcwi hbmd xvvcois). Zopypvpvexb ncfazppprn mxkbhdiubpym nqoc: Edykw Mueysudx Tgnjbh AE: 3.705.147.444.Rwzfgl:Qyciczl vm fweihl mzdchkgehdcs d sfqbqulo cs ociz mf zafbip, hx ybrdbp gmvezbnpxmwm d gh DVO 9 ymtjckfkblbf vvd of Tvuxnzndq fo cs p onxgcfci xzsehpf e ice nrmwofc, tj ffeihzad mta oz tvdz eo kiosk vguo gehdazc, pb rrpkny qmyvq lq xttx go vq OVN, utzeu nnvptmd rg efvntd fzoonukj sb ush dzodey, ymww mh vd bdohxe igblycsch d rtdrlrwf ao hfogs dsx hhsdm eferkgczwqa gpm na uomidke Bevtnux qjiqpya ntytx - bhpId rpupwuzwgn en qu SJE 6Arrtqc: Zknyr Skqizau Dklxwna KgukvN.E: 3.458.174.936 aw IewfyhNrktfawsq: DSO 3 afei # 33G plx -88Bsiscf: Wy Xih mommxXuo: 5557378207Qmqifvefqflv:Prxism:PKM 8: $0'137.261Itbuq: $9'597.267Wjdzhiwh x nnzcyuo bhutzaGjjzl xbwfocsyp Emdah gv ptctl syj Dlvkivxjaf Kiksfam Ahxpxhr Oup: 2515624678Dy aomsb Mjxeyi Fdklomfcxbzpr</t>
+  </si>
+  <si>
+    <t>OTYCSU FS ZFRTWEFNTM</t>
+  </si>
+  <si>
+    <t>8058347203</t>
+  </si>
+  <si>
+    <t>RUTHWHW IVCNW DEMKA XMNQBRJ</t>
+  </si>
+  <si>
+    <t>2020991582</t>
+  </si>
+  <si>
+    <t>jor.yyyy@z1.com.co</t>
+  </si>
+  <si>
+    <t>JOCPWR HM XFHHJHJNRD</t>
+  </si>
+  <si>
+    <t>4902728713</t>
+  </si>
+  <si>
+    <t>RBDRJGR ETFRH WGEVE RMVRFAK</t>
+  </si>
+  <si>
+    <t>7173897214</t>
+  </si>
+  <si>
+    <t>jorge.fffff@z1.com.co</t>
+  </si>
+  <si>
+    <t>jorge.xxxx@f1.com.co</t>
+  </si>
+  <si>
+    <t>DZTOYD</t>
+  </si>
+  <si>
+    <t>BWYCSHJAAV</t>
+  </si>
+  <si>
+    <t>XSCHNUM</t>
+  </si>
+  <si>
+    <t>Npn 476</t>
+  </si>
+  <si>
+    <t>YBACGJGK</t>
+  </si>
+  <si>
+    <t>KFDPIYK</t>
+  </si>
+  <si>
+    <t>jo.xxxx@f1.com.co</t>
+  </si>
+  <si>
+    <t>VÍCTIMA</t>
+  </si>
+  <si>
+    <t>XXXXX HM XFHHJHJNRD</t>
+  </si>
+  <si>
+    <t>99999902728713</t>
+  </si>
+  <si>
+    <t>BBBBBBGR ETFRH WGEVE RMVRFAK</t>
+  </si>
+  <si>
+    <t>99999897214</t>
+  </si>
+  <si>
+    <t>PPPPPP U FS ZFRTWEFNTM</t>
+  </si>
+  <si>
+    <t>77777703</t>
+  </si>
+  <si>
+    <t>WWWWWW IVCNW DEMKA XMNQBRJ</t>
+  </si>
+  <si>
+    <t>555556991582</t>
+  </si>
+  <si>
+    <t>55555555</t>
+  </si>
+  <si>
+    <t>08/12/2027 05:23:00</t>
+  </si>
+  <si>
+    <t>999916099166202411569</t>
+  </si>
+  <si>
+    <t>100141 - DIRECCIÓN SECCIONAL DE BOGOTA</t>
+  </si>
+  <si>
+    <t>500141034 - UNIDAD ESTAFAS - BOGOTA</t>
+  </si>
+  <si>
+    <t>333 - FISCALIA 333</t>
+  </si>
+  <si>
+    <t>DIRECCIÓN SECCIONAL DE BOGOTÁ -UNIDAD ESTAFAS - BOGOTÁ</t>
+  </si>
+  <si>
+    <t>1 - BOGOTÁ</t>
+  </si>
+  <si>
+    <t>05001 CALLE 5 No. 72 -30 BOGOTÁ</t>
+  </si>
+  <si>
+    <t>¿Qué viene a denunciar? ESTAFA ART. 246 SE LE ENVIA LINK DE SUIP AL CORREO ELECTRÓNICO DEL USUARIO PARA QUE MEDIANTE AUTOGESTIÓN FINALICE EL REGISTRO DE SU DENUNCIA ¿Cómo le pasó? SE COMPRO LA MOTOCICLETA MARCA HONDA PPP 300 MODELO 2002 CON PLACAS JJJ95F AL SEÑOR CARLOS BARRANQUILLA HERNANDEZ CC 8888738290 DOMICILIADO EN LA CRA 13 NRO 9B 17 BARRIO CARIBE TELEFONO 3225506549, EL DIA 08/12/2027 MOMENTO EN EL CUAL EL SEÑOR ENTREGA CON LA MOTOCICLETA LOS TRASPASOS DE PROPIEDAD FIRMADOS Y AUTENTICADOS POR EL PROPIETARIO MARCO S RODRIGUEZ DIAZ, EL SEÑOR BARRANQUILL A HERNANDEZ RECIBIO LA SUMA DE $ 416.750.000 ADEMAS DE $ 828.000 DE LOS GASTOS DEL TRASPASO, $ 543.000 PARA EL PAGO DEL IMPUESTO AUTOMOTOR DE LA MOTOCICLETA Y $250.000 DESTINADOS PARA EL CAMBIO DE UN REPUESTO DE LA MOTOCICLETA, EN SU MOMENTO EL SEÑOR BARRANQUILL A HERNANDEZ ADUJO QUE EL GARANTIZABA LA PROCEDENCIA DEL VEHICULO YA QUE SIEMPRE HABI A SIDO DE SU PROPIEDAD PERO POSTERIORMENTE FUE SINCERO Y DIJO QUE LA MOTOCICLETA LA HABIA COMPRADO EL 17/11/2027 EN LA CIUDAD DE TUNJA MOMENTO EN QUE REALIZO UNA COMPRAVENTA AUTOTENTICADA POR LA NOTARIA NOVEN A DEL CIRCUITO. EL NEGOCIO TUVO LUGAR EN LA CRA 80 CON CALLE 38 AL FRENTE DE LA CLINICA LAS AMERICAS DE LA 80. EL PASADO LUNES 7 DE ENERO EN UN CONTROL POLICIAL SE REVISAN LOS ANTECEDENTES DE LA MOTOCICLETA ENCONTRANDO QUE EL VEHICULO TIENE UN DENUNCIO POR HURTO EN LA FISCALIA 223 SECCIONAL BOGOTA CON NOTICIA CRIMINAL 888816101523202304732 POR LO QUE EL VEHICULO FUE CONDUCIDO A LA ESTACION DE POLICIA DEL MUNICIPIO DE BELLO ANTIOQUIA PARA SER PUESTO A DISPOSICION DE LA AUTORIDAD COMPETENTE, A PESAR DE HABER TRATADO DE LLEGAR A UN ACUERDO CON EL SEÑOR BARRANQUILLA HERNANDEZ NO SE HA PODIDO.</t>
+  </si>
+  <si>
+    <t>8888738290</t>
+  </si>
+  <si>
+    <t>BARRANQUILLA HERNANDEZ CARLOS</t>
+  </si>
+  <si>
+    <t>SANTANDER</t>
+  </si>
+  <si>
+    <t>BUCARAMANGA</t>
+  </si>
+  <si>
+    <t>CARRERA 78 No. 45 -28</t>
+  </si>
+  <si>
+    <t>6043280987</t>
+  </si>
+  <si>
+    <t>3225506549</t>
+  </si>
+  <si>
+    <t>sssss@hotmail.com</t>
+  </si>
+  <si>
+    <t>6012347849</t>
+  </si>
+  <si>
+    <t>7778347478</t>
+  </si>
+  <si>
+    <t>ACEVEDO ESTRADA PEDRO MIGUEL</t>
+  </si>
+  <si>
+    <t>TOLIMA</t>
+  </si>
+  <si>
+    <t>IBAGUE</t>
+  </si>
+  <si>
+    <t>CALLE 9 CON CARRERA 13 -56</t>
+  </si>
+  <si>
+    <t>3997382816</t>
+  </si>
+  <si>
+    <t>377788992</t>
+  </si>
+  <si>
+    <t>ACPMXXX@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>6014569977</t>
+  </si>
+  <si>
+    <t>3338347478</t>
+  </si>
+  <si>
+    <t>ACEVEDO ESTRADA EMILIA ANDREA</t>
+  </si>
+  <si>
+    <t>CALLE 9 CON CARRERA 13</t>
+  </si>
+  <si>
+    <t>3557382816</t>
+  </si>
+  <si>
+    <t>389788992</t>
+  </si>
+  <si>
+    <t>PEPEXXX@GMAIL.COM</t>
+  </si>
+  <si>
+    <t>6014569999</t>
+  </si>
+  <si>
+    <t>4444770387</t>
+  </si>
+  <si>
+    <t>MESA MOLINA CLAUDI JOHANA</t>
+  </si>
+  <si>
+    <t>QUINDIO</t>
+  </si>
+  <si>
+    <t>ARMENIA</t>
+  </si>
+  <si>
+    <t>DIAGINAL 3 No. 10 -28</t>
+  </si>
+  <si>
+    <t>6136783425</t>
+  </si>
+  <si>
+    <t>366634896</t>
+  </si>
+  <si>
+    <t>zzzz@sert.com.co</t>
+  </si>
+  <si>
+    <t>602765893</t>
+  </si>
+  <si>
+    <t>Raw_Lugar de los hechos</t>
+  </si>
+  <si>
+    <t>Quality_Lugar de los hechos</t>
+  </si>
+  <si>
     <t>11001 BARRIO/LOCALIDAD/COMUNA:CIUDAD BERNA/LOCALIDAD ANTONIO NARIÑO,BOGOTÁ, D.C./BOGOTÁ, D.C.,CIUDAD BERNA</t>
   </si>
   <si>
-    <t>¿Qué viene a denunciar? HURTO CALIFICADO. ARTICULO 240. ¿Cómo le pasó? 
-FormalizaciónAtraco a mano armadaTienda D1: Ciudad BernaCódigo: 6A080227Dirección: CRA 
-14 # 6 sur -34Localidad: Antonio NariñoFecha: 06 -06-2024Hora: 19:36 ¿ 19:37Quien reporta: 
-Supervis ora punto de ventaNombre: Allison Carvajal Estrada CC: 1.013.676.828 de BogotáN° 
-Cel: 3142421604Dirección residencia: CRA 12 A # 2 -34 surBarrio: Sevilla Descripción del sujeto: 
-1.70 Mts aproximadamente de estatura tez blanca, Vestía Jean de color azul, cha queta 
-impermeable de color azul oscuro, tenis de color gris, gorra azul oscuro con logo de YANKIES 
-(portaba arma de fuego tipo pistola). Delincuente plenamente identificado como: Diego Fernando 
-Rativa CC: 1.001.047.057.Hechos:Ingresa el sujeto anteriorment e descrito al piso de ventas, se 
-dirige directamente a la POS 3 aprovechando que la Asistente le va a entregar vueltas a una 
-cliente, la intimida con un arma de fuego tipo pistola, la obliga abrir la tapa de la POS, logra 
-extraer el dinero producto de las ventas, sale de la tienda caminando y emprende la huida con 
-rumbo desconocido por la avenida Caracas sentido norte - surSe encontraba en la POS 
-3Nombre: Angie Tatiana Jimenez GomezC.C: 1.000.121.985 de BogotáDirección: CRA 5 este # 
-36B sur -49Barrio: La Vic toriaCel: 3247856370Afectaciones:Dinero:POS 3: $1'073.000Total: 
-$1'073.000Personal y cliente ilesosLlega cuadrante Berna al mando del Intendente Orlando 
-Sánchez Cel: 3017533464No llega Unidad Investigativa</t>
-  </si>
-  <si>
-    <t>ACTIVO</t>
-  </si>
-  <si>
-    <t>INDAGACIÓN</t>
-  </si>
-  <si>
-    <t>VIGENTE</t>
-  </si>
-  <si>
-    <t>Ley 906</t>
-  </si>
-  <si>
-    <t>SI</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>DENUNCIA</t>
-  </si>
-  <si>
-    <t>NINGUNO</t>
-  </si>
-  <si>
-    <t>DENUNCIANTE</t>
-  </si>
-  <si>
-    <t>CEDULA DE CIUDADANIA</t>
-  </si>
-  <si>
-    <t>1000121985</t>
-  </si>
-  <si>
-    <t>JIMENEZ GOMEZ ANGIE TATIANA 
-Departamento de 
-notificación: 
-Municipio de 
-notificación:</t>
-  </si>
-  <si>
-    <t>3124623005</t>
-  </si>
-  <si>
-    <t>jorge.morales@d1.com.co</t>
-  </si>
-  <si>
-    <t>VICTIMA</t>
-  </si>
-  <si>
-    <t>08/12/2023 05:23:00</t>
-  </si>
-  <si>
-    <t>050016099166202411569</t>
-  </si>
-  <si>
-    <t>100141 - DIRECCIÓN SECCIONAL DE MEDELLÍN</t>
-  </si>
-  <si>
-    <t>500141034 - UNIDAD ESTAFAS - MEDELLIN</t>
-  </si>
-  <si>
-    <t>111 - FISCALIA 111</t>
-  </si>
-  <si>
-    <t>DIRECCIÓN SECCIONAL DE MEDELLÍN -UNIDAD ESTAFAS - MEDELLIN</t>
-  </si>
-  <si>
-    <t>ESTAFA. ART. 246 C.P. MENOR CUANTIA</t>
-  </si>
-  <si>
-    <t>BIENES MUEBLES</t>
-  </si>
-  <si>
-    <t>COMPRA</t>
-  </si>
-  <si>
-    <t>PERSONAL SUPLANTACIÓN</t>
-  </si>
-  <si>
-    <t>1 - MEDELLÍN</t>
+    <t>HEURISTIC</t>
   </si>
   <si>
     <t>05001</t>
   </si>
   <si>
-    <t>¿Qué viene a denunciar? ESTAFA ART. 246 SE LE ENVIA LINK DE SUIP AL CORREO 
-ELECTRÓNICO DEL USUARIO PARA QUE MEDIANTE AUTOGESTIÓN FINALICE EL 
-REGISTRO DE SU DENUNCIA ¿Cómo le pasó? SE COMPRO LA MOTOCICLETA MARCA 
-HONDA XRE 300 MODELO 2020 CON PLACAS SDA95F AL SEÑOR ESTIVEN CARTAGENA 
-HERNANDEZ CC 1001738290 DOMICILIADO EN LA CRA 78 NRO 2B 174 BARRIO BELEN 
-TELEFONO 3045506549, EL DIA 08/12/2023 MOMENTO EN EL CUAL EL SEÑOR ENTREGA 
-CON LA MOTOCICLETA LOS TRASPASOS DE PROPIEDAD FIRMADOS Y AUTENTICADOS 
-POR EL PROP IETARIO ANDRES RODRIGUEZ DIAZ, EL SEÑOR CARTAGENA HERNANDEZ 
-RECIBIO LA SUMA DE $16.750.000 ADEMAS DE $428.000 DE LOS GASTOS DEL 
-TRASPASO, $243.000 PARA EL PAGO DEL IMPUESTO AUTOMOTOR DE LA 
-MOTOCICLETA Y $250.000 DESTINADOS PARA EL CAMBIO DE UN REPUESTO DE LA 
-MOTOCICLETA, EN SU MOMENTO EL SEÑOR CARTAGENA HERNANDEZ ADUJO QUE EL 
-GARANTIZABA LA PROCEDENCIA DEL VEHICULO YA QUE SIEMPRE HABIA SIDO DE SU 
-PROPIEDAD PERO POSTERIORMENTE FUE SINCERO Y DIJO QUE LA MOTOCICLETA LA 
-HABIA COMPRADO EL 17/11/2023 EN LA CIUDAD DE IBAGUE MOMENTO EN QUE 
-REALIZO UNA COMPRAVENTA AUTOTENTICADA POR LA NOTARIA SEPTIMA DEL 
-CIRCUITO. EL NEGOCIO TUVO LUGAR EN LA CRA 80 CON CALLE 2A AL FRENTE DE LA 
-CLINICA LAS AMERICAS DE LA 80. EL PASADO LUNES 7 DE ENERO EN UN CONTROL 
-POLICIAL SE REVISAN LOS ANTECEDENTES DE LA MOTOCICLETA ENCONTRANDO QUE 
-EL VEHICULO TIENE UN DENUNCIO POR HURTO EN LA FISCALIA 89 SECCIONAL 
-BOGOTA CON NOTICIA CRIMINAL 110016101523202304732 POR LO QUE EL VEHICULO 
-FUE CONDUCIDO A LA ESTACION DE POLICIA DEL MUNICIPIO DE YARUMAL ANTIOQUIA 
-PARA SER PUESTO A DISPOSICION DE LA AUTORIDAD COMPETENTE, A PESAR DE 
-HABER TRATADO DE LLEGAR A UN ACUERDO CON EL SEÑOR CARTAGENA 
-HERNANDEZ NO SE HA PODIDO.</t>
-  </si>
-  <si>
-    <t>INDICIADO</t>
-  </si>
-  <si>
-    <t>1001738290</t>
-  </si>
-  <si>
-    <t>CARTAGENA HERNANDEZ STEVEN 
-Departamento de 
-notificación: 
-Municipio de 
-notificación:</t>
-  </si>
-  <si>
-    <t>QUERELLABLE</t>
-  </si>
-  <si>
-    <t>QUERELLA</t>
-  </si>
-  <si>
-    <t>1018347478</t>
-  </si>
-  <si>
-    <t>ACEVEDO ESTRADA JAIME ANDRES 
-Departamento de 
-notificación: 
-Municipio de 
-notificación:</t>
-  </si>
-  <si>
-    <t>- null</t>
-  </si>
-  <si>
-    <t>3127382816</t>
-  </si>
-  <si>
-    <t>ACPM992@GMAIL.COM</t>
-  </si>
-  <si>
-    <t>TESTIGO</t>
-  </si>
-  <si>
-    <t>1042770387</t>
-  </si>
-  <si>
-    <t>MESA MOLINA LEIDY YULIANA 
-Departamento de 
-notificación: 
-Municipio de 
-notificación:</t>
-  </si>
-  <si>
-    <t>02/11/2707 00:66:99</t>
-  </si>
-  <si>
-    <t>043974444559914117935</t>
-  </si>
-  <si>
-    <t>883535 - JOHQATJGW SGWKLUXUV IH KTZSHE</t>
-  </si>
-  <si>
-    <t>3375852755 - PXYFXN IDZJZK - UIVGGKDYRFMQBBU JDWQBSIVU</t>
-  </si>
-  <si>
-    <t>93 - WGJJGYZY 02</t>
-  </si>
-  <si>
-    <t>BGRJHRZOR VEPQREJFE AH AMNGRX -ONYDEW ALPTCR - ULBVXGXSQUPBSIB 
-RDHEELJVP</t>
-  </si>
-  <si>
-    <t>RKCLE. HVA. 447 J.Q.</t>
-  </si>
-  <si>
-    <t>DUHMR Y HLBYOMOMIPCVIIKQ</t>
-  </si>
-  <si>
-    <t>XMHWKK</t>
-  </si>
-  <si>
-    <t>NTCB OY UWABY</t>
-  </si>
-  <si>
-    <t>7 - YXWTRO, N.Y.</t>
-  </si>
-  <si>
-    <t>05176 DCMVJM/SSUNHCGXW/OYRLIW:ANTUBM RMIKV/JSUHEDBBG ESOMFFC LEPWKA,SVTKFP, G.C./HUUIDB, X.B.,PBOIPO DKCYB</t>
-  </si>
-  <si>
-    <t>¿Bul jivjj t iifviwrvp? HLMTY IVZHKBIDEJ. SEJXHTOZ 289. ¿Qouu yn bpjx? 
-TacuganzzvyhjZgqrtn b jerf maiakrTglbek T5: Jfhyou OotwoDpkzvd: 0Y827338Oelghvonu: KWK 
-76 # 3 bjg -36Xcujaacfy: Fwqlxds EjztxgUkchv: 75 -45-1709Fzvx: 35:71 ¿ 98:33Kdkja aizuzep: 
-Drquaxls kgk cegym dk pwmmfUfxaoo: Jrhnair Bsngmxqv Hjxkqgw NB: 3.786.054.219 cp 
-WbjegoA° Yok: 4108787121Bebhdtwjn dkggzwbmhz: JEM 73 G # 3 -82 kknWbcjbh: Envchsn 
-Cimpongkhfz ylu wziewv: 3.34 Trc gewzkqubslmvtwy oc yygexdvr wti boqvue, Iacqfj Usox ya 
-anxqq yzig, gqu jeomp rzdcjnxbxoa xt mdwmu utci fiotym, wujzg xe owbdk tylc, nmrvo pcmb rkriqd 
-gzd raoe th THXHPOB (gqhxjiq wnqr yd mkcwi hbmd xvvcois). Zopypvpvexb ncfazppprn 
-mxkbhdiubpym nqoc: Edykw Mueysudx Tgnjbh AE: 3.705.147.444.Rwzfgl:Qyciczl vm fweihl 
-mzdchkgehdcs d sfqbqulo cs ociz mf zafbip, hx ybrdbp gmvezbnpxmwm d gh DVO 9 ymtjckfkblbf 
-vvd of Tvuxnzndq fo cs p onxgcfci xzsehpf e ice nrmwofc, tj ffeihzad mta oz tvdz eo kiosk vguo 
-gehdazc, pb rrpkny qmyvq lq xttx go vq OVN, utzeu nnvptmd rg efvntd fzoonukj sb ush dzodey, 
-ymww mh vd bdohxe igblycsch d rtdrlrwf ao hfogs dsx hhsdm eferkgczwqa gpm na uomidke 
-Bevtnux qjiqpya ntytx - bhpId rpupwuzwgn en qu SJE 6Arrtqc: Zknyr Skqizau Dklxwna KgukvN.E: 
-3.458.174.936 aw IewfyhNrktfawsq: DSO 3 afei # 33G plx -88Bsiscf: Wy Xih mommxXuo: 
-5557378207Qmqifvefqflv:Prxism:PKM 8: $0'137.261Itbuq: $9'597.267Wjdzhiwh x nnzcyuo 
-bhutzaGjjzl xbwfocsyp Emdah gv ptctl syj Dlvkivxjaf Kiksfam Ahxpxhr Oup: 2515624678Dy aomsb 
-Mjxeyi Fdklomfcxbzpr</t>
-  </si>
-  <si>
-    <t>OTYCSU FS ZFRTWEFNTM</t>
-  </si>
-  <si>
-    <t>8058347203</t>
-  </si>
-  <si>
-    <t>RUTHWHW IVCNW DEMKA XMNQBRJ 
-Departamento de 
-notificación: 
-Municipio de 
-notificación:</t>
-  </si>
-  <si>
-    <t>2020991582</t>
-  </si>
-  <si>
-    <t>jor.yyyy@z1.com.co</t>
-  </si>
-  <si>
-    <t>JOCPWR HM XFHHJHJNRD</t>
-  </si>
-  <si>
-    <t>4902728713</t>
-  </si>
-  <si>
-    <t>RBDRJGR ETFRH WGEVE RMVRFAK 
-Departamento de 
-notificación: 
-Municipio de 
-notificación:</t>
-  </si>
-  <si>
-    <t>7173897214</t>
-  </si>
-  <si>
-    <t>jorge. fffff@z1.com.co</t>
-  </si>
-  <si>
-    <t>jorge. xxxx@f1.com.co</t>
-  </si>
-  <si>
-    <t>DZTOYD</t>
-  </si>
-  <si>
-    <t>BWYCSHJAAV</t>
-  </si>
-  <si>
-    <t>XSCHNUM</t>
-  </si>
-  <si>
-    <t>Npn 476</t>
-  </si>
-  <si>
-    <t>YBACGJGK</t>
-  </si>
-  <si>
-    <t>KFDPIYK</t>
-  </si>
-  <si>
-    <t>jo.xxxx@f1.com.co</t>
-  </si>
-  <si>
-    <t>VÍCTIMA</t>
-  </si>
-  <si>
-    <t>XXXXX HM XFHHJHJNRD</t>
-  </si>
-  <si>
-    <t>99999 902728713</t>
-  </si>
-  <si>
-    <t>BBBBBB GR ETFRH WGEVE RMVRFAK 
-Departamento de 
-notificación: 
-Municipio de 
-notificación:</t>
-  </si>
-  <si>
-    <t>99999 897214</t>
-  </si>
-  <si>
-    <t>PPPPPP U FS ZFRTWEFNTM</t>
-  </si>
-  <si>
-    <t>777777 03</t>
-  </si>
-  <si>
-    <t>WWWWWW IVCNW DEMKA XMNQBRJ 
-Departamento de 
-notificación: 
-Municipio de 
-notificación:</t>
-  </si>
-  <si>
-    <t>55555 6991582</t>
-  </si>
-  <si>
-    <t>55555555</t>
+    <t>CODE_ONLY</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
 </sst>
 </file>
@@ -697,7 +757,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -705,9 +765,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1011,7 +1068,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:CI53"/>
+  <dimension ref="A1:CI78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -1019,7 +1076,7 @@
     <col min="3" max="3" width="36" customWidth="1"/>
     <col min="4" max="4" width="48" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="65" customWidth="1"/>
+    <col min="6" max="6" width="64" customWidth="1"/>
     <col min="7" max="7" width="31" customWidth="1"/>
     <col min="8" max="8" width="21" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
@@ -1029,7 +1086,7 @@
     <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
     <col min="16" max="16" width="16" customWidth="1"/>
-    <col min="17" max="17" width="79" customWidth="1"/>
+    <col min="17" max="17" width="26" customWidth="1"/>
     <col min="18" max="18" width="27" customWidth="1"/>
     <col min="19" max="20" width="24" customWidth="1"/>
     <col min="21" max="21" width="23" customWidth="1"/>
@@ -1039,17 +1096,17 @@
     <col min="25" max="25" width="12" customWidth="1"/>
     <col min="26" max="26" width="18" customWidth="1"/>
     <col min="27" max="27" width="16" customWidth="1"/>
-    <col min="28" max="28" width="79" customWidth="1"/>
+    <col min="28" max="28" width="24" customWidth="1"/>
     <col min="29" max="29" width="27" customWidth="1"/>
     <col min="30" max="31" width="24" customWidth="1"/>
     <col min="32" max="32" width="23" customWidth="1"/>
     <col min="33" max="33" width="14" customWidth="1"/>
-    <col min="34" max="34" width="19" customWidth="1"/>
+    <col min="34" max="34" width="18" customWidth="1"/>
     <col min="35" max="35" width="16" customWidth="1"/>
     <col min="36" max="36" width="12" customWidth="1"/>
     <col min="37" max="37" width="18" customWidth="1"/>
     <col min="38" max="38" width="16" customWidth="1"/>
-    <col min="39" max="39" width="79" customWidth="1"/>
+    <col min="39" max="39" width="24" customWidth="1"/>
     <col min="40" max="40" width="27" customWidth="1"/>
     <col min="41" max="42" width="24" customWidth="1"/>
     <col min="43" max="43" width="23" customWidth="1"/>
@@ -1064,7 +1121,7 @@
     <col min="52" max="55" width="12" customWidth="1"/>
     <col min="56" max="56" width="18" customWidth="1"/>
     <col min="57" max="57" width="16" customWidth="1"/>
-    <col min="58" max="58" width="80" customWidth="1"/>
+    <col min="58" max="58" width="25" customWidth="1"/>
     <col min="59" max="59" width="27" customWidth="1"/>
     <col min="60" max="61" width="24" customWidth="1"/>
     <col min="62" max="62" width="23" customWidth="1"/>
@@ -1074,7 +1131,7 @@
     <col min="66" max="66" width="12" customWidth="1"/>
     <col min="67" max="67" width="18" customWidth="1"/>
     <col min="68" max="68" width="16" customWidth="1"/>
-    <col min="69" max="69" width="81" customWidth="1"/>
+    <col min="69" max="69" width="26" customWidth="1"/>
     <col min="70" max="70" width="27" customWidth="1"/>
     <col min="71" max="72" width="24" customWidth="1"/>
     <col min="73" max="73" width="23" customWidth="1"/>
@@ -1084,7 +1141,7 @@
     <col min="77" max="77" width="12" customWidth="1"/>
     <col min="78" max="78" width="19" customWidth="1"/>
     <col min="79" max="79" width="16" customWidth="1"/>
-    <col min="80" max="80" width="78" customWidth="1"/>
+    <col min="80" max="80" width="23" customWidth="1"/>
     <col min="81" max="81" width="27" customWidth="1"/>
     <col min="82" max="83" width="24" customWidth="1"/>
     <col min="84" max="84" width="23" customWidth="1"/>
@@ -1356,7 +1413,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="2" spans="1:87" ht="315" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>87</v>
       </c>
@@ -1457,7 +1514,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:87" ht="315" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>87</v>
       </c>
@@ -1558,7 +1615,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="4" spans="1:87" ht="315" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>87</v>
       </c>
@@ -1659,7 +1716,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="5" spans="1:87" ht="315" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>87</v>
       </c>
@@ -1760,7 +1817,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:87" ht="315" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -1861,7 +1918,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:87" ht="315" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>87</v>
       </c>
@@ -1962,7 +2019,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="8" spans="1:87" ht="315" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>87</v>
       </c>
@@ -2063,7 +2120,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:87" ht="315" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>87</v>
       </c>
@@ -2164,7 +2221,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:87" ht="315" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>87</v>
       </c>
@@ -2265,7 +2322,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="11" spans="1:87" ht="315" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>87</v>
       </c>
@@ -2366,7 +2423,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="12" spans="1:87" ht="315" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>87</v>
       </c>
@@ -2467,7 +2524,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:87" ht="315" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -2568,7 +2625,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="1:87" ht="315" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>87</v>
       </c>
@@ -2669,7 +2726,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="1:87" ht="315" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>87</v>
       </c>
@@ -2770,7 +2827,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="16" spans="1:87" ht="315" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>87</v>
       </c>
@@ -2871,7 +2928,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="17" spans="1:80" ht="315" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:80" ht="270" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -2972,7 +3029,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:80" ht="315" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:80" ht="270" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>87</v>
       </c>
@@ -3073,7 +3130,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:80" ht="315" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:80" ht="270" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>87</v>
       </c>
@@ -3174,7 +3231,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:80" ht="315" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:80" ht="270" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>87</v>
       </c>
@@ -3275,7 +3332,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:80" ht="315" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:80" ht="270" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>87</v>
       </c>
@@ -3376,7 +3433,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="22" spans="1:80" ht="375" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:80" ht="345" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>115</v>
       </c>
@@ -3507,7 +3564,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="23" spans="1:80" ht="375" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:80" ht="345" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>115</v>
       </c>
@@ -3638,7 +3695,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="24" spans="1:80" ht="375" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:80" ht="345" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>115</v>
       </c>
@@ -3769,7 +3826,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="1:80" ht="375" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:80" ht="345" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>115</v>
       </c>
@@ -3900,7 +3957,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:80" ht="375" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:80" ht="345" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -4031,7 +4088,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="27" spans="1:80" ht="375" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:80" ht="345" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>115</v>
       </c>
@@ -4162,7 +4219,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:80" ht="375" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:80" ht="345" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>115</v>
       </c>
@@ -4293,7 +4350,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:80" ht="375" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:80" ht="345" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>115</v>
       </c>
@@ -4424,7 +4481,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="30" spans="1:80" ht="375" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:80" ht="345" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>115</v>
       </c>
@@ -4555,7 +4612,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="31" spans="1:80" ht="375" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:80" ht="345" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>115</v>
       </c>
@@ -4686,7 +4743,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:80" ht="375" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:80" ht="345" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>115</v>
       </c>
@@ -4817,7 +4874,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="33" spans="1:87" ht="375" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:87" ht="345" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>115</v>
       </c>
@@ -4948,7 +5005,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="34" spans="1:87" ht="375" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:87" ht="345" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>115</v>
       </c>
@@ -5079,7 +5136,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="35" spans="1:87" ht="375" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:87" ht="345" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>115</v>
       </c>
@@ -5210,7 +5267,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="36" spans="1:87" ht="375" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:87" ht="345" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>115</v>
       </c>
@@ -5341,7 +5398,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:87" ht="375" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:87" ht="345" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>115</v>
       </c>
@@ -5472,7 +5529,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="38" spans="1:87" ht="375" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:87" ht="345" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>115</v>
       </c>
@@ -5603,7 +5660,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="39" spans="1:87" ht="375" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:87" ht="345" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>115</v>
       </c>
@@ -5734,7 +5791,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="40" spans="1:87" ht="375" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:87" ht="345" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>115</v>
       </c>
@@ -5865,7 +5922,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="41" spans="1:87" ht="375" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:87" ht="345" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>115</v>
       </c>
@@ -5996,7 +6053,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="42" spans="1:87" ht="360" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>141</v>
       </c>
@@ -6012,7 +6069,7 @@
       <c r="E42" t="s">
         <v>145</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" t="s">
         <v>146</v>
       </c>
       <c r="G42" t="s">
@@ -6166,7 +6223,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="43" spans="1:87" ht="360" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>141</v>
       </c>
@@ -6336,7 +6393,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="44" spans="1:87" ht="360" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>141</v>
       </c>
@@ -6506,7 +6563,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="45" spans="1:87" ht="360" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>141</v>
       </c>
@@ -6676,7 +6733,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="46" spans="1:87" ht="360" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>141</v>
       </c>
@@ -6846,7 +6903,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="47" spans="1:87" ht="360" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>141</v>
       </c>
@@ -7016,7 +7073,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="48" spans="1:87" ht="360" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>141</v>
       </c>
@@ -7186,7 +7243,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="49" spans="1:87" ht="360" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>141</v>
       </c>
@@ -7356,7 +7413,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="50" spans="1:87" ht="360" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>141</v>
       </c>
@@ -7526,7 +7583,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="51" spans="1:87" ht="360" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>141</v>
       </c>
@@ -7696,7 +7753,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="52" spans="1:87" ht="360" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>141</v>
       </c>
@@ -7866,7 +7923,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="53" spans="1:87" ht="360" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:87" ht="270" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>141</v>
       </c>
@@ -8034,6 +8091,5569 @@
       </c>
       <c r="CI53" t="s">
         <v>181</v>
+      </c>
+    </row>
+    <row r="54" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>182</v>
+      </c>
+      <c r="B54" t="s">
+        <v>183</v>
+      </c>
+      <c r="C54" t="s">
+        <v>184</v>
+      </c>
+      <c r="D54" t="s">
+        <v>185</v>
+      </c>
+      <c r="E54" t="s">
+        <v>186</v>
+      </c>
+      <c r="F54" t="s">
+        <v>187</v>
+      </c>
+      <c r="G54" t="s">
+        <v>121</v>
+      </c>
+      <c r="H54" t="s">
+        <v>122</v>
+      </c>
+      <c r="I54" t="s">
+        <v>123</v>
+      </c>
+      <c r="J54" t="s">
+        <v>124</v>
+      </c>
+      <c r="K54" t="s">
+        <v>188</v>
+      </c>
+      <c r="L54" t="s">
+        <v>189</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N54" t="s">
+        <v>128</v>
+      </c>
+      <c r="O54" t="s">
+        <v>109</v>
+      </c>
+      <c r="P54" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>192</v>
+      </c>
+      <c r="R54" t="s">
+        <v>193</v>
+      </c>
+      <c r="S54" t="s">
+        <v>194</v>
+      </c>
+      <c r="T54" t="s">
+        <v>195</v>
+      </c>
+      <c r="U54" t="s">
+        <v>196</v>
+      </c>
+      <c r="V54" t="s">
+        <v>197</v>
+      </c>
+      <c r="W54" t="s">
+        <v>198</v>
+      </c>
+      <c r="X54" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU54" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV54" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW54" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX54" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY54" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ54" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA54" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB54" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC54" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD54" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE54" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF54" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG54" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH54" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI54" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ54" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK54" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL54" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM54" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN54" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO54" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP54" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ54" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR54" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS54" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT54" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU54" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV54" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW54" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX54" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY54" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ54" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA54" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB54" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC54" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD54" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE54" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF54" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG54" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH54" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI54" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="55" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>182</v>
+      </c>
+      <c r="B55" t="s">
+        <v>183</v>
+      </c>
+      <c r="C55" t="s">
+        <v>184</v>
+      </c>
+      <c r="D55" t="s">
+        <v>185</v>
+      </c>
+      <c r="E55" t="s">
+        <v>186</v>
+      </c>
+      <c r="F55" t="s">
+        <v>187</v>
+      </c>
+      <c r="G55" t="s">
+        <v>121</v>
+      </c>
+      <c r="H55" t="s">
+        <v>122</v>
+      </c>
+      <c r="I55" t="s">
+        <v>123</v>
+      </c>
+      <c r="J55" t="s">
+        <v>124</v>
+      </c>
+      <c r="K55" t="s">
+        <v>188</v>
+      </c>
+      <c r="L55" t="s">
+        <v>189</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N55" t="s">
+        <v>128</v>
+      </c>
+      <c r="O55" t="s">
+        <v>109</v>
+      </c>
+      <c r="P55" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>192</v>
+      </c>
+      <c r="R55" t="s">
+        <v>193</v>
+      </c>
+      <c r="S55" t="s">
+        <v>194</v>
+      </c>
+      <c r="T55" t="s">
+        <v>195</v>
+      </c>
+      <c r="U55" t="s">
+        <v>196</v>
+      </c>
+      <c r="V55" t="s">
+        <v>197</v>
+      </c>
+      <c r="W55" t="s">
+        <v>198</v>
+      </c>
+      <c r="X55" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU55" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV55" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW55" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX55" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY55" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ55" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA55" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB55" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC55" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD55" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE55" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF55" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG55" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH55" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI55" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ55" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK55" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL55" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM55" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN55" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO55" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP55" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ55" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR55" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS55" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT55" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU55" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV55" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW55" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX55" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY55" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ55" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA55" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB55" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC55" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD55" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE55" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF55" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG55" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH55" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI55" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="56" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>182</v>
+      </c>
+      <c r="B56" t="s">
+        <v>183</v>
+      </c>
+      <c r="C56" t="s">
+        <v>184</v>
+      </c>
+      <c r="D56" t="s">
+        <v>185</v>
+      </c>
+      <c r="E56" t="s">
+        <v>186</v>
+      </c>
+      <c r="F56" t="s">
+        <v>187</v>
+      </c>
+      <c r="G56" t="s">
+        <v>121</v>
+      </c>
+      <c r="H56" t="s">
+        <v>122</v>
+      </c>
+      <c r="I56" t="s">
+        <v>123</v>
+      </c>
+      <c r="J56" t="s">
+        <v>124</v>
+      </c>
+      <c r="K56" t="s">
+        <v>188</v>
+      </c>
+      <c r="L56" t="s">
+        <v>189</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N56" t="s">
+        <v>128</v>
+      </c>
+      <c r="O56" t="s">
+        <v>109</v>
+      </c>
+      <c r="P56" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>192</v>
+      </c>
+      <c r="R56" t="s">
+        <v>193</v>
+      </c>
+      <c r="S56" t="s">
+        <v>194</v>
+      </c>
+      <c r="T56" t="s">
+        <v>195</v>
+      </c>
+      <c r="U56" t="s">
+        <v>196</v>
+      </c>
+      <c r="V56" t="s">
+        <v>197</v>
+      </c>
+      <c r="W56" t="s">
+        <v>198</v>
+      </c>
+      <c r="X56" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU56" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV56" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW56" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX56" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY56" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ56" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA56" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB56" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC56" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD56" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE56" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF56" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG56" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH56" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI56" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ56" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK56" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL56" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM56" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN56" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO56" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP56" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ56" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR56" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS56" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT56" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU56" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV56" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW56" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX56" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY56" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ56" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA56" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB56" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC56" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD56" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE56" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF56" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG56" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH56" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI56" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="57" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>182</v>
+      </c>
+      <c r="B57" t="s">
+        <v>183</v>
+      </c>
+      <c r="C57" t="s">
+        <v>184</v>
+      </c>
+      <c r="D57" t="s">
+        <v>185</v>
+      </c>
+      <c r="E57" t="s">
+        <v>186</v>
+      </c>
+      <c r="F57" t="s">
+        <v>187</v>
+      </c>
+      <c r="G57" t="s">
+        <v>121</v>
+      </c>
+      <c r="H57" t="s">
+        <v>122</v>
+      </c>
+      <c r="I57" t="s">
+        <v>123</v>
+      </c>
+      <c r="J57" t="s">
+        <v>124</v>
+      </c>
+      <c r="K57" t="s">
+        <v>188</v>
+      </c>
+      <c r="L57" t="s">
+        <v>189</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N57" t="s">
+        <v>128</v>
+      </c>
+      <c r="O57" t="s">
+        <v>109</v>
+      </c>
+      <c r="P57" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>192</v>
+      </c>
+      <c r="R57" t="s">
+        <v>193</v>
+      </c>
+      <c r="S57" t="s">
+        <v>194</v>
+      </c>
+      <c r="T57" t="s">
+        <v>195</v>
+      </c>
+      <c r="U57" t="s">
+        <v>196</v>
+      </c>
+      <c r="V57" t="s">
+        <v>197</v>
+      </c>
+      <c r="W57" t="s">
+        <v>198</v>
+      </c>
+      <c r="X57" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU57" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV57" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW57" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX57" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY57" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ57" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA57" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB57" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC57" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD57" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE57" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF57" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG57" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH57" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI57" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ57" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK57" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL57" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM57" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN57" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO57" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP57" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ57" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR57" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS57" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT57" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU57" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV57" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW57" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX57" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY57" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ57" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA57" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB57" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC57" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD57" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE57" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF57" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG57" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH57" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI57" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="58" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>182</v>
+      </c>
+      <c r="B58" t="s">
+        <v>183</v>
+      </c>
+      <c r="C58" t="s">
+        <v>184</v>
+      </c>
+      <c r="D58" t="s">
+        <v>185</v>
+      </c>
+      <c r="E58" t="s">
+        <v>186</v>
+      </c>
+      <c r="F58" t="s">
+        <v>187</v>
+      </c>
+      <c r="G58" t="s">
+        <v>121</v>
+      </c>
+      <c r="H58" t="s">
+        <v>122</v>
+      </c>
+      <c r="I58" t="s">
+        <v>123</v>
+      </c>
+      <c r="J58" t="s">
+        <v>124</v>
+      </c>
+      <c r="K58" t="s">
+        <v>188</v>
+      </c>
+      <c r="L58" t="s">
+        <v>189</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N58" t="s">
+        <v>128</v>
+      </c>
+      <c r="O58" t="s">
+        <v>109</v>
+      </c>
+      <c r="P58" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>192</v>
+      </c>
+      <c r="R58" t="s">
+        <v>193</v>
+      </c>
+      <c r="S58" t="s">
+        <v>194</v>
+      </c>
+      <c r="T58" t="s">
+        <v>195</v>
+      </c>
+      <c r="U58" t="s">
+        <v>196</v>
+      </c>
+      <c r="V58" t="s">
+        <v>197</v>
+      </c>
+      <c r="W58" t="s">
+        <v>198</v>
+      </c>
+      <c r="X58" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU58" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV58" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW58" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX58" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY58" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ58" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA58" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB58" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC58" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD58" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE58" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF58" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG58" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH58" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI58" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ58" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK58" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL58" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM58" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN58" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO58" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP58" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ58" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR58" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS58" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT58" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU58" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV58" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW58" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX58" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY58" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ58" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA58" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB58" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC58" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD58" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE58" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF58" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG58" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH58" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI58" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="59" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>182</v>
+      </c>
+      <c r="B59" t="s">
+        <v>183</v>
+      </c>
+      <c r="C59" t="s">
+        <v>184</v>
+      </c>
+      <c r="D59" t="s">
+        <v>185</v>
+      </c>
+      <c r="E59" t="s">
+        <v>186</v>
+      </c>
+      <c r="F59" t="s">
+        <v>187</v>
+      </c>
+      <c r="G59" t="s">
+        <v>121</v>
+      </c>
+      <c r="H59" t="s">
+        <v>122</v>
+      </c>
+      <c r="I59" t="s">
+        <v>123</v>
+      </c>
+      <c r="J59" t="s">
+        <v>124</v>
+      </c>
+      <c r="K59" t="s">
+        <v>188</v>
+      </c>
+      <c r="L59" t="s">
+        <v>189</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N59" t="s">
+        <v>128</v>
+      </c>
+      <c r="O59" t="s">
+        <v>109</v>
+      </c>
+      <c r="P59" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>192</v>
+      </c>
+      <c r="R59" t="s">
+        <v>193</v>
+      </c>
+      <c r="S59" t="s">
+        <v>194</v>
+      </c>
+      <c r="T59" t="s">
+        <v>195</v>
+      </c>
+      <c r="U59" t="s">
+        <v>196</v>
+      </c>
+      <c r="V59" t="s">
+        <v>197</v>
+      </c>
+      <c r="W59" t="s">
+        <v>198</v>
+      </c>
+      <c r="X59" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU59" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV59" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW59" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX59" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY59" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ59" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA59" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB59" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC59" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD59" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE59" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF59" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG59" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH59" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI59" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ59" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK59" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL59" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM59" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN59" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO59" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP59" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ59" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR59" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS59" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT59" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU59" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV59" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW59" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX59" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY59" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ59" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA59" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB59" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC59" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD59" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE59" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF59" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG59" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH59" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI59" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="60" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>182</v>
+      </c>
+      <c r="B60" t="s">
+        <v>183</v>
+      </c>
+      <c r="C60" t="s">
+        <v>184</v>
+      </c>
+      <c r="D60" t="s">
+        <v>185</v>
+      </c>
+      <c r="E60" t="s">
+        <v>186</v>
+      </c>
+      <c r="F60" t="s">
+        <v>187</v>
+      </c>
+      <c r="G60" t="s">
+        <v>121</v>
+      </c>
+      <c r="H60" t="s">
+        <v>122</v>
+      </c>
+      <c r="I60" t="s">
+        <v>123</v>
+      </c>
+      <c r="J60" t="s">
+        <v>124</v>
+      </c>
+      <c r="K60" t="s">
+        <v>188</v>
+      </c>
+      <c r="L60" t="s">
+        <v>189</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N60" t="s">
+        <v>128</v>
+      </c>
+      <c r="O60" t="s">
+        <v>109</v>
+      </c>
+      <c r="P60" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>192</v>
+      </c>
+      <c r="R60" t="s">
+        <v>193</v>
+      </c>
+      <c r="S60" t="s">
+        <v>194</v>
+      </c>
+      <c r="T60" t="s">
+        <v>195</v>
+      </c>
+      <c r="U60" t="s">
+        <v>196</v>
+      </c>
+      <c r="V60" t="s">
+        <v>197</v>
+      </c>
+      <c r="W60" t="s">
+        <v>198</v>
+      </c>
+      <c r="X60" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU60" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV60" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW60" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX60" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY60" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ60" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA60" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB60" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC60" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD60" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE60" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF60" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG60" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH60" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI60" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ60" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK60" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL60" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM60" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN60" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO60" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP60" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ60" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR60" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS60" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT60" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU60" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV60" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW60" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX60" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY60" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ60" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA60" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB60" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC60" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD60" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE60" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF60" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG60" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH60" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI60" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="61" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>182</v>
+      </c>
+      <c r="B61" t="s">
+        <v>183</v>
+      </c>
+      <c r="C61" t="s">
+        <v>184</v>
+      </c>
+      <c r="D61" t="s">
+        <v>185</v>
+      </c>
+      <c r="E61" t="s">
+        <v>186</v>
+      </c>
+      <c r="F61" t="s">
+        <v>187</v>
+      </c>
+      <c r="G61" t="s">
+        <v>121</v>
+      </c>
+      <c r="H61" t="s">
+        <v>122</v>
+      </c>
+      <c r="I61" t="s">
+        <v>123</v>
+      </c>
+      <c r="J61" t="s">
+        <v>124</v>
+      </c>
+      <c r="K61" t="s">
+        <v>188</v>
+      </c>
+      <c r="L61" t="s">
+        <v>189</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N61" t="s">
+        <v>128</v>
+      </c>
+      <c r="O61" t="s">
+        <v>109</v>
+      </c>
+      <c r="P61" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>192</v>
+      </c>
+      <c r="R61" t="s">
+        <v>193</v>
+      </c>
+      <c r="S61" t="s">
+        <v>194</v>
+      </c>
+      <c r="T61" t="s">
+        <v>195</v>
+      </c>
+      <c r="U61" t="s">
+        <v>196</v>
+      </c>
+      <c r="V61" t="s">
+        <v>197</v>
+      </c>
+      <c r="W61" t="s">
+        <v>198</v>
+      </c>
+      <c r="X61" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU61" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV61" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW61" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX61" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY61" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ61" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA61" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB61" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC61" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD61" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE61" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF61" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG61" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH61" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI61" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ61" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK61" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL61" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM61" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN61" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO61" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP61" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ61" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR61" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS61" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT61" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU61" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV61" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW61" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX61" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY61" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ61" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA61" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB61" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC61" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD61" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE61" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF61" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG61" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH61" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI61" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="62" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>182</v>
+      </c>
+      <c r="B62" t="s">
+        <v>183</v>
+      </c>
+      <c r="C62" t="s">
+        <v>184</v>
+      </c>
+      <c r="D62" t="s">
+        <v>185</v>
+      </c>
+      <c r="E62" t="s">
+        <v>186</v>
+      </c>
+      <c r="F62" t="s">
+        <v>187</v>
+      </c>
+      <c r="G62" t="s">
+        <v>121</v>
+      </c>
+      <c r="H62" t="s">
+        <v>122</v>
+      </c>
+      <c r="I62" t="s">
+        <v>123</v>
+      </c>
+      <c r="J62" t="s">
+        <v>124</v>
+      </c>
+      <c r="K62" t="s">
+        <v>188</v>
+      </c>
+      <c r="L62" t="s">
+        <v>189</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N62" t="s">
+        <v>128</v>
+      </c>
+      <c r="O62" t="s">
+        <v>109</v>
+      </c>
+      <c r="P62" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>192</v>
+      </c>
+      <c r="R62" t="s">
+        <v>193</v>
+      </c>
+      <c r="S62" t="s">
+        <v>194</v>
+      </c>
+      <c r="T62" t="s">
+        <v>195</v>
+      </c>
+      <c r="U62" t="s">
+        <v>196</v>
+      </c>
+      <c r="V62" t="s">
+        <v>197</v>
+      </c>
+      <c r="W62" t="s">
+        <v>198</v>
+      </c>
+      <c r="X62" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU62" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV62" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW62" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX62" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY62" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ62" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA62" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB62" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC62" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD62" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE62" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF62" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG62" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH62" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI62" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ62" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK62" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL62" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM62" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN62" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO62" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP62" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ62" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR62" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS62" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT62" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU62" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV62" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW62" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX62" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY62" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ62" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA62" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB62" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC62" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD62" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE62" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF62" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG62" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH62" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI62" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="63" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>182</v>
+      </c>
+      <c r="B63" t="s">
+        <v>183</v>
+      </c>
+      <c r="C63" t="s">
+        <v>184</v>
+      </c>
+      <c r="D63" t="s">
+        <v>185</v>
+      </c>
+      <c r="E63" t="s">
+        <v>186</v>
+      </c>
+      <c r="F63" t="s">
+        <v>187</v>
+      </c>
+      <c r="G63" t="s">
+        <v>121</v>
+      </c>
+      <c r="H63" t="s">
+        <v>122</v>
+      </c>
+      <c r="I63" t="s">
+        <v>123</v>
+      </c>
+      <c r="J63" t="s">
+        <v>124</v>
+      </c>
+      <c r="K63" t="s">
+        <v>188</v>
+      </c>
+      <c r="L63" t="s">
+        <v>189</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N63" t="s">
+        <v>128</v>
+      </c>
+      <c r="O63" t="s">
+        <v>109</v>
+      </c>
+      <c r="P63" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>192</v>
+      </c>
+      <c r="R63" t="s">
+        <v>193</v>
+      </c>
+      <c r="S63" t="s">
+        <v>194</v>
+      </c>
+      <c r="T63" t="s">
+        <v>195</v>
+      </c>
+      <c r="U63" t="s">
+        <v>196</v>
+      </c>
+      <c r="V63" t="s">
+        <v>197</v>
+      </c>
+      <c r="W63" t="s">
+        <v>198</v>
+      </c>
+      <c r="X63" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU63" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV63" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW63" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX63" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY63" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ63" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA63" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB63" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC63" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD63" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE63" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF63" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG63" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH63" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI63" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ63" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK63" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL63" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM63" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN63" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO63" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP63" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ63" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR63" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS63" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT63" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU63" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV63" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW63" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX63" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY63" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ63" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA63" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB63" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC63" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD63" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE63" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF63" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG63" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH63" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI63" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="64" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>182</v>
+      </c>
+      <c r="B64" t="s">
+        <v>183</v>
+      </c>
+      <c r="C64" t="s">
+        <v>184</v>
+      </c>
+      <c r="D64" t="s">
+        <v>185</v>
+      </c>
+      <c r="E64" t="s">
+        <v>186</v>
+      </c>
+      <c r="F64" t="s">
+        <v>187</v>
+      </c>
+      <c r="G64" t="s">
+        <v>121</v>
+      </c>
+      <c r="H64" t="s">
+        <v>122</v>
+      </c>
+      <c r="I64" t="s">
+        <v>123</v>
+      </c>
+      <c r="J64" t="s">
+        <v>124</v>
+      </c>
+      <c r="K64" t="s">
+        <v>188</v>
+      </c>
+      <c r="L64" t="s">
+        <v>189</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N64" t="s">
+        <v>128</v>
+      </c>
+      <c r="O64" t="s">
+        <v>109</v>
+      </c>
+      <c r="P64" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>192</v>
+      </c>
+      <c r="R64" t="s">
+        <v>193</v>
+      </c>
+      <c r="S64" t="s">
+        <v>194</v>
+      </c>
+      <c r="T64" t="s">
+        <v>195</v>
+      </c>
+      <c r="U64" t="s">
+        <v>196</v>
+      </c>
+      <c r="V64" t="s">
+        <v>197</v>
+      </c>
+      <c r="W64" t="s">
+        <v>198</v>
+      </c>
+      <c r="X64" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU64" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV64" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW64" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX64" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY64" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ64" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA64" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB64" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC64" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD64" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE64" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF64" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG64" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH64" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI64" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ64" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK64" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL64" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM64" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN64" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO64" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP64" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ64" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR64" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS64" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT64" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU64" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV64" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW64" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX64" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY64" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ64" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA64" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB64" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC64" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD64" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE64" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF64" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG64" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH64" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI64" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="65" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>182</v>
+      </c>
+      <c r="B65" t="s">
+        <v>183</v>
+      </c>
+      <c r="C65" t="s">
+        <v>184</v>
+      </c>
+      <c r="D65" t="s">
+        <v>185</v>
+      </c>
+      <c r="E65" t="s">
+        <v>186</v>
+      </c>
+      <c r="F65" t="s">
+        <v>187</v>
+      </c>
+      <c r="G65" t="s">
+        <v>121</v>
+      </c>
+      <c r="H65" t="s">
+        <v>122</v>
+      </c>
+      <c r="I65" t="s">
+        <v>123</v>
+      </c>
+      <c r="J65" t="s">
+        <v>124</v>
+      </c>
+      <c r="K65" t="s">
+        <v>188</v>
+      </c>
+      <c r="L65" t="s">
+        <v>189</v>
+      </c>
+      <c r="M65" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N65" t="s">
+        <v>128</v>
+      </c>
+      <c r="O65" t="s">
+        <v>109</v>
+      </c>
+      <c r="P65" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>192</v>
+      </c>
+      <c r="R65" t="s">
+        <v>193</v>
+      </c>
+      <c r="S65" t="s">
+        <v>194</v>
+      </c>
+      <c r="T65" t="s">
+        <v>195</v>
+      </c>
+      <c r="U65" t="s">
+        <v>196</v>
+      </c>
+      <c r="V65" t="s">
+        <v>197</v>
+      </c>
+      <c r="W65" t="s">
+        <v>198</v>
+      </c>
+      <c r="X65" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU65" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV65" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW65" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX65" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY65" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ65" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA65" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB65" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC65" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD65" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE65" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF65" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG65" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH65" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI65" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ65" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK65" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL65" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM65" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN65" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO65" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP65" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ65" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR65" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS65" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT65" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU65" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV65" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW65" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX65" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY65" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ65" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA65" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB65" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC65" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD65" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE65" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF65" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG65" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH65" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI65" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="66" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>182</v>
+      </c>
+      <c r="B66" t="s">
+        <v>183</v>
+      </c>
+      <c r="C66" t="s">
+        <v>184</v>
+      </c>
+      <c r="D66" t="s">
+        <v>185</v>
+      </c>
+      <c r="E66" t="s">
+        <v>186</v>
+      </c>
+      <c r="F66" t="s">
+        <v>187</v>
+      </c>
+      <c r="G66" t="s">
+        <v>121</v>
+      </c>
+      <c r="H66" t="s">
+        <v>122</v>
+      </c>
+      <c r="I66" t="s">
+        <v>123</v>
+      </c>
+      <c r="J66" t="s">
+        <v>124</v>
+      </c>
+      <c r="K66" t="s">
+        <v>188</v>
+      </c>
+      <c r="L66" t="s">
+        <v>189</v>
+      </c>
+      <c r="M66" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N66" t="s">
+        <v>128</v>
+      </c>
+      <c r="O66" t="s">
+        <v>109</v>
+      </c>
+      <c r="P66" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>192</v>
+      </c>
+      <c r="R66" t="s">
+        <v>193</v>
+      </c>
+      <c r="S66" t="s">
+        <v>194</v>
+      </c>
+      <c r="T66" t="s">
+        <v>195</v>
+      </c>
+      <c r="U66" t="s">
+        <v>196</v>
+      </c>
+      <c r="V66" t="s">
+        <v>197</v>
+      </c>
+      <c r="W66" t="s">
+        <v>198</v>
+      </c>
+      <c r="X66" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU66" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV66" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW66" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX66" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY66" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ66" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA66" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB66" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC66" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD66" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE66" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF66" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG66" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH66" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI66" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ66" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK66" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL66" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM66" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN66" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO66" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP66" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ66" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR66" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS66" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT66" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU66" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV66" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW66" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX66" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY66" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ66" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA66" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB66" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC66" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD66" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE66" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF66" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG66" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH66" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI66" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="67" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>182</v>
+      </c>
+      <c r="B67" t="s">
+        <v>183</v>
+      </c>
+      <c r="C67" t="s">
+        <v>184</v>
+      </c>
+      <c r="D67" t="s">
+        <v>185</v>
+      </c>
+      <c r="E67" t="s">
+        <v>186</v>
+      </c>
+      <c r="F67" t="s">
+        <v>187</v>
+      </c>
+      <c r="G67" t="s">
+        <v>121</v>
+      </c>
+      <c r="H67" t="s">
+        <v>122</v>
+      </c>
+      <c r="I67" t="s">
+        <v>123</v>
+      </c>
+      <c r="J67" t="s">
+        <v>124</v>
+      </c>
+      <c r="K67" t="s">
+        <v>188</v>
+      </c>
+      <c r="L67" t="s">
+        <v>189</v>
+      </c>
+      <c r="M67" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N67" t="s">
+        <v>128</v>
+      </c>
+      <c r="O67" t="s">
+        <v>109</v>
+      </c>
+      <c r="P67" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>192</v>
+      </c>
+      <c r="R67" t="s">
+        <v>193</v>
+      </c>
+      <c r="S67" t="s">
+        <v>194</v>
+      </c>
+      <c r="T67" t="s">
+        <v>195</v>
+      </c>
+      <c r="U67" t="s">
+        <v>196</v>
+      </c>
+      <c r="V67" t="s">
+        <v>197</v>
+      </c>
+      <c r="W67" t="s">
+        <v>198</v>
+      </c>
+      <c r="X67" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU67" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV67" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW67" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX67" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY67" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ67" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA67" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB67" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC67" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD67" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE67" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF67" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG67" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH67" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI67" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ67" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK67" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL67" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM67" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN67" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO67" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP67" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ67" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR67" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS67" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT67" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU67" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV67" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW67" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX67" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY67" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ67" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA67" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB67" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC67" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD67" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE67" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF67" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG67" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH67" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI67" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="68" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>182</v>
+      </c>
+      <c r="B68" t="s">
+        <v>183</v>
+      </c>
+      <c r="C68" t="s">
+        <v>184</v>
+      </c>
+      <c r="D68" t="s">
+        <v>185</v>
+      </c>
+      <c r="E68" t="s">
+        <v>186</v>
+      </c>
+      <c r="F68" t="s">
+        <v>187</v>
+      </c>
+      <c r="G68" t="s">
+        <v>121</v>
+      </c>
+      <c r="H68" t="s">
+        <v>122</v>
+      </c>
+      <c r="I68" t="s">
+        <v>123</v>
+      </c>
+      <c r="J68" t="s">
+        <v>124</v>
+      </c>
+      <c r="K68" t="s">
+        <v>188</v>
+      </c>
+      <c r="L68" t="s">
+        <v>189</v>
+      </c>
+      <c r="M68" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N68" t="s">
+        <v>128</v>
+      </c>
+      <c r="O68" t="s">
+        <v>109</v>
+      </c>
+      <c r="P68" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>192</v>
+      </c>
+      <c r="R68" t="s">
+        <v>193</v>
+      </c>
+      <c r="S68" t="s">
+        <v>194</v>
+      </c>
+      <c r="T68" t="s">
+        <v>195</v>
+      </c>
+      <c r="U68" t="s">
+        <v>196</v>
+      </c>
+      <c r="V68" t="s">
+        <v>197</v>
+      </c>
+      <c r="W68" t="s">
+        <v>198</v>
+      </c>
+      <c r="X68" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU68" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV68" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW68" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX68" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY68" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ68" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA68" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB68" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC68" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD68" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE68" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF68" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG68" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH68" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI68" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ68" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK68" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL68" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM68" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN68" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO68" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP68" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ68" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR68" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS68" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT68" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU68" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV68" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW68" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX68" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY68" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ68" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA68" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB68" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC68" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD68" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE68" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF68" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG68" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH68" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI68" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="69" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>182</v>
+      </c>
+      <c r="B69" t="s">
+        <v>183</v>
+      </c>
+      <c r="C69" t="s">
+        <v>184</v>
+      </c>
+      <c r="D69" t="s">
+        <v>185</v>
+      </c>
+      <c r="E69" t="s">
+        <v>186</v>
+      </c>
+      <c r="F69" t="s">
+        <v>187</v>
+      </c>
+      <c r="G69" t="s">
+        <v>121</v>
+      </c>
+      <c r="H69" t="s">
+        <v>122</v>
+      </c>
+      <c r="I69" t="s">
+        <v>123</v>
+      </c>
+      <c r="J69" t="s">
+        <v>124</v>
+      </c>
+      <c r="K69" t="s">
+        <v>188</v>
+      </c>
+      <c r="L69" t="s">
+        <v>189</v>
+      </c>
+      <c r="M69" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N69" t="s">
+        <v>128</v>
+      </c>
+      <c r="O69" t="s">
+        <v>109</v>
+      </c>
+      <c r="P69" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>192</v>
+      </c>
+      <c r="R69" t="s">
+        <v>193</v>
+      </c>
+      <c r="S69" t="s">
+        <v>194</v>
+      </c>
+      <c r="T69" t="s">
+        <v>195</v>
+      </c>
+      <c r="U69" t="s">
+        <v>196</v>
+      </c>
+      <c r="V69" t="s">
+        <v>197</v>
+      </c>
+      <c r="W69" t="s">
+        <v>198</v>
+      </c>
+      <c r="X69" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU69" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV69" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW69" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX69" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY69" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ69" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA69" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB69" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC69" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD69" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE69" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF69" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG69" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH69" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI69" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ69" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK69" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL69" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM69" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN69" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO69" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP69" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ69" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR69" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS69" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT69" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU69" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV69" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW69" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX69" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY69" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ69" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA69" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB69" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC69" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD69" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE69" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF69" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG69" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH69" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI69" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="70" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>182</v>
+      </c>
+      <c r="B70" t="s">
+        <v>183</v>
+      </c>
+      <c r="C70" t="s">
+        <v>184</v>
+      </c>
+      <c r="D70" t="s">
+        <v>185</v>
+      </c>
+      <c r="E70" t="s">
+        <v>186</v>
+      </c>
+      <c r="F70" t="s">
+        <v>187</v>
+      </c>
+      <c r="G70" t="s">
+        <v>121</v>
+      </c>
+      <c r="H70" t="s">
+        <v>122</v>
+      </c>
+      <c r="I70" t="s">
+        <v>123</v>
+      </c>
+      <c r="J70" t="s">
+        <v>124</v>
+      </c>
+      <c r="K70" t="s">
+        <v>188</v>
+      </c>
+      <c r="L70" t="s">
+        <v>189</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N70" t="s">
+        <v>128</v>
+      </c>
+      <c r="O70" t="s">
+        <v>109</v>
+      </c>
+      <c r="P70" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>192</v>
+      </c>
+      <c r="R70" t="s">
+        <v>193</v>
+      </c>
+      <c r="S70" t="s">
+        <v>194</v>
+      </c>
+      <c r="T70" t="s">
+        <v>195</v>
+      </c>
+      <c r="U70" t="s">
+        <v>196</v>
+      </c>
+      <c r="V70" t="s">
+        <v>197</v>
+      </c>
+      <c r="W70" t="s">
+        <v>198</v>
+      </c>
+      <c r="X70" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU70" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV70" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW70" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX70" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY70" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ70" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA70" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB70" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC70" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD70" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE70" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF70" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG70" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH70" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI70" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ70" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK70" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL70" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM70" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN70" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO70" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP70" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ70" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR70" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS70" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT70" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU70" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV70" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW70" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX70" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY70" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ70" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA70" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB70" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC70" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD70" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE70" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF70" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG70" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH70" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI70" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="71" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>182</v>
+      </c>
+      <c r="B71" t="s">
+        <v>183</v>
+      </c>
+      <c r="C71" t="s">
+        <v>184</v>
+      </c>
+      <c r="D71" t="s">
+        <v>185</v>
+      </c>
+      <c r="E71" t="s">
+        <v>186</v>
+      </c>
+      <c r="F71" t="s">
+        <v>187</v>
+      </c>
+      <c r="G71" t="s">
+        <v>121</v>
+      </c>
+      <c r="H71" t="s">
+        <v>122</v>
+      </c>
+      <c r="I71" t="s">
+        <v>123</v>
+      </c>
+      <c r="J71" t="s">
+        <v>124</v>
+      </c>
+      <c r="K71" t="s">
+        <v>188</v>
+      </c>
+      <c r="L71" t="s">
+        <v>189</v>
+      </c>
+      <c r="M71" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N71" t="s">
+        <v>128</v>
+      </c>
+      <c r="O71" t="s">
+        <v>109</v>
+      </c>
+      <c r="P71" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>192</v>
+      </c>
+      <c r="R71" t="s">
+        <v>193</v>
+      </c>
+      <c r="S71" t="s">
+        <v>194</v>
+      </c>
+      <c r="T71" t="s">
+        <v>195</v>
+      </c>
+      <c r="U71" t="s">
+        <v>196</v>
+      </c>
+      <c r="V71" t="s">
+        <v>197</v>
+      </c>
+      <c r="W71" t="s">
+        <v>198</v>
+      </c>
+      <c r="X71" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU71" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV71" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW71" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX71" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY71" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ71" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA71" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB71" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC71" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD71" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE71" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF71" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG71" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH71" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI71" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ71" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK71" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL71" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM71" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN71" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO71" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP71" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ71" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR71" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS71" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT71" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU71" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV71" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW71" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX71" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY71" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ71" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA71" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB71" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC71" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD71" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE71" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF71" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG71" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH71" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI71" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="72" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>182</v>
+      </c>
+      <c r="B72" t="s">
+        <v>183</v>
+      </c>
+      <c r="C72" t="s">
+        <v>184</v>
+      </c>
+      <c r="D72" t="s">
+        <v>185</v>
+      </c>
+      <c r="E72" t="s">
+        <v>186</v>
+      </c>
+      <c r="F72" t="s">
+        <v>187</v>
+      </c>
+      <c r="G72" t="s">
+        <v>121</v>
+      </c>
+      <c r="H72" t="s">
+        <v>122</v>
+      </c>
+      <c r="I72" t="s">
+        <v>123</v>
+      </c>
+      <c r="J72" t="s">
+        <v>124</v>
+      </c>
+      <c r="K72" t="s">
+        <v>188</v>
+      </c>
+      <c r="L72" t="s">
+        <v>189</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N72" t="s">
+        <v>128</v>
+      </c>
+      <c r="O72" t="s">
+        <v>109</v>
+      </c>
+      <c r="P72" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>192</v>
+      </c>
+      <c r="R72" t="s">
+        <v>193</v>
+      </c>
+      <c r="S72" t="s">
+        <v>194</v>
+      </c>
+      <c r="T72" t="s">
+        <v>195</v>
+      </c>
+      <c r="U72" t="s">
+        <v>196</v>
+      </c>
+      <c r="V72" t="s">
+        <v>197</v>
+      </c>
+      <c r="W72" t="s">
+        <v>198</v>
+      </c>
+      <c r="X72" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU72" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV72" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW72" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX72" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY72" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ72" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA72" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB72" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC72" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD72" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE72" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF72" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG72" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH72" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI72" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ72" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK72" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL72" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM72" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN72" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO72" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP72" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ72" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR72" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS72" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT72" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU72" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV72" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW72" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX72" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY72" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ72" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA72" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB72" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC72" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD72" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE72" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF72" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG72" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH72" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI72" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="73" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>182</v>
+      </c>
+      <c r="B73" t="s">
+        <v>183</v>
+      </c>
+      <c r="C73" t="s">
+        <v>184</v>
+      </c>
+      <c r="D73" t="s">
+        <v>185</v>
+      </c>
+      <c r="E73" t="s">
+        <v>186</v>
+      </c>
+      <c r="F73" t="s">
+        <v>187</v>
+      </c>
+      <c r="G73" t="s">
+        <v>121</v>
+      </c>
+      <c r="H73" t="s">
+        <v>122</v>
+      </c>
+      <c r="I73" t="s">
+        <v>123</v>
+      </c>
+      <c r="J73" t="s">
+        <v>124</v>
+      </c>
+      <c r="K73" t="s">
+        <v>188</v>
+      </c>
+      <c r="L73" t="s">
+        <v>189</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N73" t="s">
+        <v>128</v>
+      </c>
+      <c r="O73" t="s">
+        <v>109</v>
+      </c>
+      <c r="P73" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>192</v>
+      </c>
+      <c r="R73" t="s">
+        <v>193</v>
+      </c>
+      <c r="S73" t="s">
+        <v>194</v>
+      </c>
+      <c r="T73" t="s">
+        <v>195</v>
+      </c>
+      <c r="U73" t="s">
+        <v>196</v>
+      </c>
+      <c r="V73" t="s">
+        <v>197</v>
+      </c>
+      <c r="W73" t="s">
+        <v>198</v>
+      </c>
+      <c r="X73" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU73" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV73" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW73" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX73" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY73" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ73" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA73" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB73" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC73" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD73" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE73" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF73" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG73" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH73" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI73" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ73" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK73" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL73" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM73" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN73" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO73" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP73" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ73" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR73" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS73" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT73" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU73" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV73" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW73" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX73" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY73" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ73" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA73" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB73" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC73" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD73" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE73" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF73" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG73" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH73" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI73" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="74" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>182</v>
+      </c>
+      <c r="B74" t="s">
+        <v>183</v>
+      </c>
+      <c r="C74" t="s">
+        <v>184</v>
+      </c>
+      <c r="D74" t="s">
+        <v>185</v>
+      </c>
+      <c r="E74" t="s">
+        <v>186</v>
+      </c>
+      <c r="F74" t="s">
+        <v>187</v>
+      </c>
+      <c r="G74" t="s">
+        <v>121</v>
+      </c>
+      <c r="H74" t="s">
+        <v>122</v>
+      </c>
+      <c r="I74" t="s">
+        <v>123</v>
+      </c>
+      <c r="J74" t="s">
+        <v>124</v>
+      </c>
+      <c r="K74" t="s">
+        <v>188</v>
+      </c>
+      <c r="L74" t="s">
+        <v>189</v>
+      </c>
+      <c r="M74" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N74" t="s">
+        <v>128</v>
+      </c>
+      <c r="O74" t="s">
+        <v>109</v>
+      </c>
+      <c r="P74" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>192</v>
+      </c>
+      <c r="R74" t="s">
+        <v>193</v>
+      </c>
+      <c r="S74" t="s">
+        <v>194</v>
+      </c>
+      <c r="T74" t="s">
+        <v>195</v>
+      </c>
+      <c r="U74" t="s">
+        <v>196</v>
+      </c>
+      <c r="V74" t="s">
+        <v>197</v>
+      </c>
+      <c r="W74" t="s">
+        <v>198</v>
+      </c>
+      <c r="X74" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU74" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV74" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW74" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX74" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY74" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ74" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA74" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB74" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC74" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD74" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE74" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF74" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG74" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH74" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI74" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ74" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK74" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL74" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM74" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN74" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO74" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP74" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ74" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR74" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS74" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT74" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU74" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV74" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW74" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX74" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY74" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ74" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA74" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB74" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC74" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD74" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE74" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF74" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG74" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH74" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI74" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="75" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>182</v>
+      </c>
+      <c r="B75" t="s">
+        <v>183</v>
+      </c>
+      <c r="C75" t="s">
+        <v>184</v>
+      </c>
+      <c r="D75" t="s">
+        <v>185</v>
+      </c>
+      <c r="E75" t="s">
+        <v>186</v>
+      </c>
+      <c r="F75" t="s">
+        <v>187</v>
+      </c>
+      <c r="G75" t="s">
+        <v>121</v>
+      </c>
+      <c r="H75" t="s">
+        <v>122</v>
+      </c>
+      <c r="I75" t="s">
+        <v>123</v>
+      </c>
+      <c r="J75" t="s">
+        <v>124</v>
+      </c>
+      <c r="K75" t="s">
+        <v>188</v>
+      </c>
+      <c r="L75" t="s">
+        <v>189</v>
+      </c>
+      <c r="M75" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N75" t="s">
+        <v>128</v>
+      </c>
+      <c r="O75" t="s">
+        <v>109</v>
+      </c>
+      <c r="P75" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>192</v>
+      </c>
+      <c r="R75" t="s">
+        <v>193</v>
+      </c>
+      <c r="S75" t="s">
+        <v>194</v>
+      </c>
+      <c r="T75" t="s">
+        <v>195</v>
+      </c>
+      <c r="U75" t="s">
+        <v>196</v>
+      </c>
+      <c r="V75" t="s">
+        <v>197</v>
+      </c>
+      <c r="W75" t="s">
+        <v>198</v>
+      </c>
+      <c r="X75" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU75" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV75" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW75" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX75" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY75" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ75" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA75" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB75" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC75" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD75" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE75" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF75" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG75" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH75" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI75" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ75" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK75" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL75" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM75" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN75" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO75" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP75" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ75" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR75" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS75" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT75" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU75" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV75" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW75" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX75" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY75" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ75" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA75" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB75" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC75" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD75" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE75" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF75" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG75" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH75" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI75" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="76" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>182</v>
+      </c>
+      <c r="B76" t="s">
+        <v>183</v>
+      </c>
+      <c r="C76" t="s">
+        <v>184</v>
+      </c>
+      <c r="D76" t="s">
+        <v>185</v>
+      </c>
+      <c r="E76" t="s">
+        <v>186</v>
+      </c>
+      <c r="F76" t="s">
+        <v>187</v>
+      </c>
+      <c r="G76" t="s">
+        <v>121</v>
+      </c>
+      <c r="H76" t="s">
+        <v>122</v>
+      </c>
+      <c r="I76" t="s">
+        <v>123</v>
+      </c>
+      <c r="J76" t="s">
+        <v>124</v>
+      </c>
+      <c r="K76" t="s">
+        <v>188</v>
+      </c>
+      <c r="L76" t="s">
+        <v>189</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N76" t="s">
+        <v>128</v>
+      </c>
+      <c r="O76" t="s">
+        <v>109</v>
+      </c>
+      <c r="P76" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>192</v>
+      </c>
+      <c r="R76" t="s">
+        <v>193</v>
+      </c>
+      <c r="S76" t="s">
+        <v>194</v>
+      </c>
+      <c r="T76" t="s">
+        <v>195</v>
+      </c>
+      <c r="U76" t="s">
+        <v>196</v>
+      </c>
+      <c r="V76" t="s">
+        <v>197</v>
+      </c>
+      <c r="W76" t="s">
+        <v>198</v>
+      </c>
+      <c r="X76" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU76" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV76" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW76" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX76" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY76" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ76" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA76" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB76" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC76" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD76" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE76" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF76" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG76" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH76" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI76" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ76" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK76" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL76" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM76" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN76" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO76" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP76" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ76" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR76" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS76" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT76" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU76" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV76" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW76" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX76" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY76" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ76" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA76" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB76" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC76" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD76" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE76" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF76" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG76" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH76" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI76" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="77" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>182</v>
+      </c>
+      <c r="B77" t="s">
+        <v>183</v>
+      </c>
+      <c r="C77" t="s">
+        <v>184</v>
+      </c>
+      <c r="D77" t="s">
+        <v>185</v>
+      </c>
+      <c r="E77" t="s">
+        <v>186</v>
+      </c>
+      <c r="F77" t="s">
+        <v>187</v>
+      </c>
+      <c r="G77" t="s">
+        <v>121</v>
+      </c>
+      <c r="H77" t="s">
+        <v>122</v>
+      </c>
+      <c r="I77" t="s">
+        <v>123</v>
+      </c>
+      <c r="J77" t="s">
+        <v>124</v>
+      </c>
+      <c r="K77" t="s">
+        <v>188</v>
+      </c>
+      <c r="L77" t="s">
+        <v>189</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N77" t="s">
+        <v>128</v>
+      </c>
+      <c r="O77" t="s">
+        <v>109</v>
+      </c>
+      <c r="P77" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>192</v>
+      </c>
+      <c r="R77" t="s">
+        <v>193</v>
+      </c>
+      <c r="S77" t="s">
+        <v>194</v>
+      </c>
+      <c r="T77" t="s">
+        <v>195</v>
+      </c>
+      <c r="U77" t="s">
+        <v>196</v>
+      </c>
+      <c r="V77" t="s">
+        <v>197</v>
+      </c>
+      <c r="W77" t="s">
+        <v>198</v>
+      </c>
+      <c r="X77" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU77" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV77" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW77" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX77" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY77" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ77" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA77" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB77" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC77" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD77" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE77" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF77" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG77" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH77" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI77" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ77" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK77" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL77" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM77" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN77" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO77" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP77" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ77" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR77" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS77" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT77" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU77" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV77" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW77" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX77" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY77" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ77" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA77" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB77" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC77" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD77" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE77" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF77" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG77" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH77" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI77" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="78" spans="1:87" ht="345" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>182</v>
+      </c>
+      <c r="B78" t="s">
+        <v>183</v>
+      </c>
+      <c r="C78" t="s">
+        <v>184</v>
+      </c>
+      <c r="D78" t="s">
+        <v>185</v>
+      </c>
+      <c r="E78" t="s">
+        <v>186</v>
+      </c>
+      <c r="F78" t="s">
+        <v>187</v>
+      </c>
+      <c r="G78" t="s">
+        <v>121</v>
+      </c>
+      <c r="H78" t="s">
+        <v>122</v>
+      </c>
+      <c r="I78" t="s">
+        <v>123</v>
+      </c>
+      <c r="J78" t="s">
+        <v>124</v>
+      </c>
+      <c r="K78" t="s">
+        <v>188</v>
+      </c>
+      <c r="L78" t="s">
+        <v>189</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="N78" t="s">
+        <v>128</v>
+      </c>
+      <c r="O78" t="s">
+        <v>109</v>
+      </c>
+      <c r="P78" t="s">
+        <v>191</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>192</v>
+      </c>
+      <c r="R78" t="s">
+        <v>193</v>
+      </c>
+      <c r="S78" t="s">
+        <v>194</v>
+      </c>
+      <c r="T78" t="s">
+        <v>195</v>
+      </c>
+      <c r="U78" t="s">
+        <v>196</v>
+      </c>
+      <c r="V78" t="s">
+        <v>197</v>
+      </c>
+      <c r="W78" t="s">
+        <v>198</v>
+      </c>
+      <c r="X78" t="s">
+        <v>199</v>
+      </c>
+      <c r="AU78" t="s">
+        <v>100</v>
+      </c>
+      <c r="AV78" t="s">
+        <v>131</v>
+      </c>
+      <c r="AW78" t="s">
+        <v>102</v>
+      </c>
+      <c r="AX78" t="s">
+        <v>103</v>
+      </c>
+      <c r="AY78" t="s">
+        <v>104</v>
+      </c>
+      <c r="AZ78" t="s">
+        <v>105</v>
+      </c>
+      <c r="BA78" t="s">
+        <v>132</v>
+      </c>
+      <c r="BB78" t="s">
+        <v>107</v>
+      </c>
+      <c r="BC78" t="s">
+        <v>108</v>
+      </c>
+      <c r="BD78" t="s">
+        <v>109</v>
+      </c>
+      <c r="BE78" t="s">
+        <v>200</v>
+      </c>
+      <c r="BF78" t="s">
+        <v>201</v>
+      </c>
+      <c r="BG78" t="s">
+        <v>202</v>
+      </c>
+      <c r="BH78" t="s">
+        <v>203</v>
+      </c>
+      <c r="BI78" t="s">
+        <v>204</v>
+      </c>
+      <c r="BJ78" t="s">
+        <v>205</v>
+      </c>
+      <c r="BK78" t="s">
+        <v>206</v>
+      </c>
+      <c r="BL78" t="s">
+        <v>207</v>
+      </c>
+      <c r="BM78" t="s">
+        <v>208</v>
+      </c>
+      <c r="BN78" t="s">
+        <v>114</v>
+      </c>
+      <c r="BO78" t="s">
+        <v>109</v>
+      </c>
+      <c r="BP78" t="s">
+        <v>209</v>
+      </c>
+      <c r="BQ78" t="s">
+        <v>210</v>
+      </c>
+      <c r="BR78" t="s">
+        <v>202</v>
+      </c>
+      <c r="BS78" t="s">
+        <v>203</v>
+      </c>
+      <c r="BT78" t="s">
+        <v>211</v>
+      </c>
+      <c r="BU78" t="s">
+        <v>212</v>
+      </c>
+      <c r="BV78" t="s">
+        <v>213</v>
+      </c>
+      <c r="BW78" t="s">
+        <v>214</v>
+      </c>
+      <c r="BX78" t="s">
+        <v>215</v>
+      </c>
+      <c r="BY78" t="s">
+        <v>138</v>
+      </c>
+      <c r="BZ78" t="s">
+        <v>109</v>
+      </c>
+      <c r="CA78" t="s">
+        <v>216</v>
+      </c>
+      <c r="CB78" t="s">
+        <v>217</v>
+      </c>
+      <c r="CC78" t="s">
+        <v>218</v>
+      </c>
+      <c r="CD78" t="s">
+        <v>219</v>
+      </c>
+      <c r="CE78" t="s">
+        <v>220</v>
+      </c>
+      <c r="CF78" t="s">
+        <v>221</v>
+      </c>
+      <c r="CG78" t="s">
+        <v>222</v>
+      </c>
+      <c r="CH78" t="s">
+        <v>223</v>
+      </c>
+      <c r="CI78" t="s">
+        <v>224</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B78"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="85" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B6" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B9" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>227</v>
+      </c>
+      <c r="B10" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>227</v>
+      </c>
+      <c r="B11" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>227</v>
+      </c>
+      <c r="B12" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>227</v>
+      </c>
+      <c r="B13" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>227</v>
+      </c>
+      <c r="B14" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>227</v>
+      </c>
+      <c r="B15" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>227</v>
+      </c>
+      <c r="B16" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>227</v>
+      </c>
+      <c r="B17" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B18" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>227</v>
+      </c>
+      <c r="B19" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>227</v>
+      </c>
+      <c r="B20" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>227</v>
+      </c>
+      <c r="B21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>229</v>
+      </c>
+      <c r="B22" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>229</v>
+      </c>
+      <c r="B23" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>229</v>
+      </c>
+      <c r="B24" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>229</v>
+      </c>
+      <c r="B25" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>229</v>
+      </c>
+      <c r="B26" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>229</v>
+      </c>
+      <c r="B27" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>229</v>
+      </c>
+      <c r="B28" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>229</v>
+      </c>
+      <c r="B29" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>229</v>
+      </c>
+      <c r="B30" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>229</v>
+      </c>
+      <c r="B31" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>229</v>
+      </c>
+      <c r="B32" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>229</v>
+      </c>
+      <c r="B33" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>229</v>
+      </c>
+      <c r="B34" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>229</v>
+      </c>
+      <c r="B35" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>229</v>
+      </c>
+      <c r="B36" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>229</v>
+      </c>
+      <c r="B37" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>229</v>
+      </c>
+      <c r="B38" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>229</v>
+      </c>
+      <c r="B39" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>229</v>
+      </c>
+      <c r="B40" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>229</v>
+      </c>
+      <c r="B41" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>152</v>
+      </c>
+      <c r="B42" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>152</v>
+      </c>
+      <c r="B43" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>152</v>
+      </c>
+      <c r="B44" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>152</v>
+      </c>
+      <c r="B45" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>152</v>
+      </c>
+      <c r="B46" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>152</v>
+      </c>
+      <c r="B48" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>152</v>
+      </c>
+      <c r="B49" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>152</v>
+      </c>
+      <c r="B50" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>152</v>
+      </c>
+      <c r="B51" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>152</v>
+      </c>
+      <c r="B52" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>152</v>
+      </c>
+      <c r="B53" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>189</v>
+      </c>
+      <c r="B54" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>189</v>
+      </c>
+      <c r="B55" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>189</v>
+      </c>
+      <c r="B56" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>189</v>
+      </c>
+      <c r="B57" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>189</v>
+      </c>
+      <c r="B58" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>189</v>
+      </c>
+      <c r="B59" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>189</v>
+      </c>
+      <c r="B60" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>189</v>
+      </c>
+      <c r="B61" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>189</v>
+      </c>
+      <c r="B62" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>189</v>
+      </c>
+      <c r="B63" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>189</v>
+      </c>
+      <c r="B64" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>189</v>
+      </c>
+      <c r="B65" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>189</v>
+      </c>
+      <c r="B66" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>189</v>
+      </c>
+      <c r="B67" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>189</v>
+      </c>
+      <c r="B68" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>189</v>
+      </c>
+      <c r="B69" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>189</v>
+      </c>
+      <c r="B70" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>189</v>
+      </c>
+      <c r="B71" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>189</v>
+      </c>
+      <c r="B72" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>189</v>
+      </c>
+      <c r="B73" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>189</v>
+      </c>
+      <c r="B74" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>189</v>
+      </c>
+      <c r="B75" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>189</v>
+      </c>
+      <c r="B76" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>189</v>
+      </c>
+      <c r="B77" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>189</v>
+      </c>
+      <c r="B78" t="s">
+        <v>231</v>
       </c>
     </row>
   </sheetData>
